--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海康桥路销售中心</t>
+          <t>小鹏汽车上海虹梅南路销售中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区康桥路700-800号</t>
+          <t>上海市闵行区虹梅南路3398号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海虹梅南路销售中心</t>
+          <t>小鹏汽车上海康桥路销售中心</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区虹梅南路3398号</t>
+          <t>上海市浦东新区康桥路700-800号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SAIC尚界用户中心•营口沈营公路</t>
+          <t>鸿蒙智行授权用户中心•营口工农路</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>营口市站前区沈营公路1号</t>
+          <t>营口市老边区新营路北15甲</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•营口工农路</t>
+          <t>SAIC尚界用户中心•营口沈营公路</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>营口市老边区新营路北15甲</t>
+          <t>营口市站前区沈营公路1号</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -11287,22 +11287,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11312,29 +11312,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11344,29 +11344,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
@@ -11388,17 +11388,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
@@ -11420,17 +11420,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -11452,17 +11452,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11472,29 +11472,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城体验店</t>
+          <t>小米汽车内蒙古包头市九原区稀土路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城</t>
+          <t>小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11504,29 +11504,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城体验店 → 湖州东吴银泰城</t>
+          <t>小米汽车内蒙古包头市九原区稀土路 → 小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路</t>
+          <t>湖州东吴银泰城体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
+          <t>湖州东吴银泰城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路 → 小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
+          <t>湖州东吴银泰城体验店 → 湖州东吴银泰城</t>
         </is>
       </c>
     </row>
@@ -11548,17 +11548,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 台州方林汽车城</t>
+          <t>蔚来空间 | 天津空港</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 台州方林汽车城</t>
+          <t>蔚来体验中心 | 天津空港</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11580,17 +11580,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 天津空港</t>
+          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 天津空港</t>
+          <t>蔚来体验中心 | 许昌恒力汽车园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽车园</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
+          <t>小米汽车四川省绵阳市涪城区汽车博览中心零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
+          <t>小米汽车四川绵阳涪城区汽车博览中心零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 68%</t>
+          <t>地址相似度 89%</t>
         </is>
       </c>
     </row>
@@ -11708,17 +11708,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区汽车博览中心零售中心</t>
+          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川绵阳涪城区汽车博览中心零售中心</t>
+          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 89%</t>
+          <t>地址相似度 68%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海虹梅南路销售中心</t>
+          <t>小鹏汽车上海康桥路销售中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区虹梅南路3398号</t>
+          <t>上海市浦东新区康桥路700-800号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海康桥路销售中心</t>
+          <t>小鹏汽车上海虹梅南路销售中心</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区康桥路700-800号</t>
+          <t>上海市闵行区虹梅南路3398号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11255,22 +11255,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11280,29 +11280,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -11324,17 +11324,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11344,29 +11344,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
@@ -11388,17 +11388,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
@@ -11420,17 +11420,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11440,29 +11440,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
@@ -11548,17 +11548,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 天津空港</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 天津空港</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 台州方林汽车城</t>
+          <t>蔚来空间 | 天津空港</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 台州方林汽车城</t>
+          <t>蔚来体验中心 | 天津空港</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -11110,7 +11110,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•营口工农路</t>
+          <t>SAIC尚界用户中心•营口沈营公路</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>营口市老边区新营路北15甲</t>
+          <t>营口市站前区沈营公路1号</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SAIC尚界用户中心•营口沈营公路</t>
+          <t>鸿蒙智行授权用户中心•营口工农路</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>营口市站前区沈营公路1号</t>
+          <t>营口市老边区新营路北15甲</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -11255,22 +11255,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
@@ -11292,17 +11292,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
@@ -11324,17 +11324,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
@@ -11356,17 +11356,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -11388,17 +11388,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11408,29 +11408,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11440,29 +11440,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11548,17 +11548,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 天津空港</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 天津空港</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 天津空港</t>
+          <t>蔚来中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 天津空港</t>
+          <t>蔚来体验中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 台州方林汽车城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 台州方林汽车城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区汽车博览中心零售中心</t>
+          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川绵阳涪城区汽车博览中心零售中心</t>
+          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 89%</t>
+          <t>地址相似度 68%</t>
         </is>
       </c>
     </row>
@@ -11708,17 +11708,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
+          <t>小米汽车四川省绵阳市涪城区汽车博览中心零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
+          <t>小米汽车四川绵阳涪城区汽车博览中心零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 68%</t>
+          <t>地址相似度 89%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -635,231 +635,252 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B9" s="3" t="n">
         <v>1088</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C9" s="3" t="n">
         <v>1087</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>815</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>817</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>0.2%</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>318</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C11" s="3" t="n">
         <v>316</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-2</v>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>-0.6%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>611</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>620</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>1.5%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>1156</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>1156</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B15" s="3" t="n">
         <v>518</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="3" t="n">
         <v>516</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-2</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>-0.4%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>阿斯顿·马丁</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>6.7%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>雷克萨斯</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B18" s="3" t="n">
         <v>1463</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C18" s="3" t="n">
         <v>1462</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>8528</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>8533</v>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" s="1" t="n">
+        <v>8567</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>8572</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
@@ -876,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E414"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3896,105 +3917,105 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D144" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>-1</v>
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D145" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>-1</v>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="D146" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>-1</v>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D147" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>-1</v>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>0</v>
@@ -4003,19 +4024,19 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>0</v>
@@ -4024,19 +4045,19 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>0</v>
@@ -4045,19 +4066,19 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>0</v>
@@ -4066,19 +4087,19 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>0</v>
@@ -4087,19 +4108,19 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>0</v>
@@ -4108,19 +4129,19 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>0</v>
@@ -4129,19 +4150,19 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>0</v>
@@ -4150,19 +4171,19 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>0</v>
@@ -4171,19 +4192,19 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>0</v>
@@ -4192,19 +4213,19 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>0</v>
@@ -4213,19 +4234,19 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>0</v>
@@ -4234,19 +4255,19 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>0</v>
@@ -4255,19 +4276,19 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>0</v>
@@ -4276,19 +4297,19 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>0</v>
@@ -4297,19 +4318,19 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>0</v>
@@ -4318,19 +4339,19 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>0</v>
@@ -4339,19 +4360,19 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>0</v>
@@ -4360,106 +4381,106 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E166" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D169" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D170" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E170" s="2" t="n">
-        <v>0</v>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="171">
@@ -4470,98 +4491,98 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E171" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="D172" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="E172" s="4" t="n">
-        <v>1</v>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="D173" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="E173" s="4" t="n">
-        <v>1</v>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D174" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>1</v>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>0</v>
@@ -4570,19 +4591,19 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>0</v>
@@ -4591,19 +4612,19 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>0</v>
@@ -4612,19 +4633,19 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
@@ -4633,19 +4654,19 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>0</v>
@@ -4654,19 +4675,19 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>0</v>
@@ -4675,19 +4696,19 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>0</v>
@@ -4696,19 +4717,19 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>0</v>
@@ -4717,19 +4738,19 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>0</v>
@@ -4738,19 +4759,19 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>0</v>
@@ -4759,19 +4780,19 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>0</v>
@@ -4780,19 +4801,19 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0</v>
@@ -4801,19 +4822,19 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -4822,19 +4843,19 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>0</v>
@@ -4843,19 +4864,19 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>0</v>
@@ -4864,19 +4885,19 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>0</v>
@@ -4885,19 +4906,19 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>0</v>
@@ -4906,19 +4927,19 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>0</v>
@@ -4927,19 +4948,19 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>0</v>
@@ -4948,85 +4969,85 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="D195" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="D196" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
           <t>湖南</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D194" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E194" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D195" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E195" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D196" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="E196" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E197" s="2" t="n">
-        <v>0</v>
+      <c r="C197" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5037,14 +5058,14 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>0</v>
@@ -5058,14 +5079,14 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>0</v>
@@ -5079,14 +5100,14 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>0</v>
@@ -5100,14 +5121,14 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>0</v>
@@ -5121,119 +5142,119 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D202" s="2" t="n">
+      <c r="D204" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E202" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+      <c r="E204" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D203" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="E203" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="D204" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="E204" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E205" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D206" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E206" s="3" t="n">
-        <v>-1</v>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>0</v>
@@ -5242,19 +5263,19 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>0</v>
@@ -5263,19 +5284,19 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>0</v>
@@ -5284,19 +5305,19 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>0</v>
@@ -5305,12 +5326,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
@@ -5326,19 +5347,19 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>0</v>
@@ -5347,19 +5368,19 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>0</v>
@@ -5368,19 +5389,19 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>0</v>
@@ -5389,19 +5410,19 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>0</v>
@@ -5410,19 +5431,19 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>0</v>
@@ -5431,19 +5452,19 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>0</v>
@@ -5452,19 +5473,19 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>0</v>
@@ -5473,19 +5494,19 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>0</v>
@@ -5494,19 +5515,19 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>0</v>
@@ -5515,19 +5536,19 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>0</v>
@@ -5536,19 +5557,19 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>0</v>
@@ -5557,19 +5578,19 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>0</v>
@@ -5578,19 +5599,19 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>0</v>
@@ -5599,106 +5620,106 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D227" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="E227" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D225" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E225" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D226" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E226" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="D227" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E227" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D228" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E228" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D229" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E229" s="2" t="n">
-        <v>0</v>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="230">
@@ -5709,14 +5730,14 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>0</v>
@@ -5730,14 +5751,14 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E231" s="2" t="n">
         <v>0</v>
@@ -5751,14 +5772,14 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E232" s="2" t="n">
         <v>0</v>
@@ -5772,14 +5793,14 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E233" s="2" t="n">
         <v>0</v>
@@ -5793,14 +5814,14 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E234" s="2" t="n">
         <v>0</v>
@@ -5814,14 +5835,14 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E235" s="2" t="n">
         <v>0</v>
@@ -5830,19 +5851,19 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E236" s="2" t="n">
         <v>0</v>
@@ -5851,19 +5872,19 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E237" s="2" t="n">
         <v>0</v>
@@ -5872,19 +5893,19 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>0</v>
@@ -5893,19 +5914,19 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E239" s="2" t="n">
         <v>0</v>
@@ -5914,19 +5935,19 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E240" s="2" t="n">
         <v>0</v>
@@ -5935,19 +5956,19 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E241" s="2" t="n">
         <v>0</v>
@@ -5956,12 +5977,12 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C242" s="2" t="n">
@@ -5977,7 +5998,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -5986,10 +6007,10 @@
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E243" s="2" t="n">
         <v>0</v>
@@ -5998,19 +6019,19 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E244" s="2" t="n">
         <v>0</v>
@@ -6019,19 +6040,19 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E245" s="2" t="n">
         <v>0</v>
@@ -6040,19 +6061,19 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E246" s="2" t="n">
         <v>0</v>
@@ -6061,19 +6082,19 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E247" s="2" t="n">
         <v>0</v>
@@ -6082,19 +6103,19 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E248" s="2" t="n">
         <v>0</v>
@@ -6103,19 +6124,19 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E249" s="2" t="n">
         <v>0</v>
@@ -6124,19 +6145,19 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E250" s="2" t="n">
         <v>0</v>
@@ -6145,19 +6166,19 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E251" s="2" t="n">
         <v>0</v>
@@ -6166,19 +6187,19 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E252" s="2" t="n">
         <v>0</v>
@@ -6187,19 +6208,19 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C253" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E253" s="2" t="n">
         <v>0</v>
@@ -6208,19 +6229,19 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C254" s="2" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E254" s="2" t="n">
         <v>0</v>
@@ -6229,19 +6250,19 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C255" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E255" s="2" t="n">
         <v>0</v>
@@ -6250,19 +6271,19 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E256" s="2" t="n">
         <v>0</v>
@@ -6271,19 +6292,19 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E257" s="2" t="n">
         <v>0</v>
@@ -6292,19 +6313,19 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E258" s="2" t="n">
         <v>0</v>
@@ -6313,19 +6334,19 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E259" s="2" t="n">
         <v>0</v>
@@ -6334,19 +6355,19 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D260" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E260" s="2" t="n">
         <v>0</v>
@@ -6355,19 +6376,19 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C261" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E261" s="2" t="n">
         <v>0</v>
@@ -6376,19 +6397,19 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C262" s="2" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="E262" s="2" t="n">
         <v>0</v>
@@ -6397,19 +6418,19 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C263" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E263" s="2" t="n">
         <v>0</v>
@@ -6418,19 +6439,19 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C264" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E264" s="2" t="n">
         <v>0</v>
@@ -6439,19 +6460,19 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C265" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E265" s="2" t="n">
         <v>0</v>
@@ -6460,19 +6481,19 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C266" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E266" s="2" t="n">
         <v>0</v>
@@ -6481,19 +6502,19 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6502,19 +6523,19 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6523,19 +6544,19 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E269" s="2" t="n">
         <v>0</v>
@@ -6544,12 +6565,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6565,19 +6586,19 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E271" s="2" t="n">
         <v>0</v>
@@ -6586,7 +6607,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -6595,10 +6616,10 @@
         </is>
       </c>
       <c r="C272" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E272" s="2" t="n">
         <v>0</v>
@@ -6607,7 +6628,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -6616,10 +6637,10 @@
         </is>
       </c>
       <c r="C273" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E273" s="2" t="n">
         <v>0</v>
@@ -6628,19 +6649,19 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E274" s="2" t="n">
         <v>0</v>
@@ -6654,182 +6675,182 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D275" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D276" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D277" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D275" s="2" t="n">
+      <c r="D278" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E275" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="4" t="inlineStr">
+      <c r="E278" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D276" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="E276" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="4" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="D277" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="E277" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="4" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D280" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C278" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D278" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E278" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="4" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D281" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D279" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="E279" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D280" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E280" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="n">
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D281" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="E281" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="D282" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="E282" s="4" t="n">
-        <v>2</v>
+      <c r="D282" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6838,19 +6859,19 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6859,19 +6880,19 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6880,19 +6901,19 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6901,19 +6922,19 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6922,19 +6943,19 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6943,19 +6964,19 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6964,19 +6985,19 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -6985,19 +7006,19 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7006,19 +7027,19 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7027,19 +7048,19 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7048,19 +7069,19 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7069,19 +7090,19 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7090,19 +7111,19 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7111,19 +7132,19 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7132,169 +7153,169 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B299" s="2" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C299" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D299" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E299" s="2" t="n">
-        <v>0</v>
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D299" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E299" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="D300" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="E300" s="2" t="n">
-        <v>0</v>
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D300" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="E300" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B301" s="2" t="inlineStr">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D301" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E301" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E302" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="D301" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="E301" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D302" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E302" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D303" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E303" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D304" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="E304" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D305" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E305" s="2" t="n">
-        <v>0</v>
+      <c r="C305" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="D305" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="E305" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -7305,14 +7326,14 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -7326,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -7347,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>0</v>
@@ -7368,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7389,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7452,77 +7473,77 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="D314" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="E314" s="3" t="n">
-        <v>-1</v>
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B315" s="3" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C315" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D315" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="E315" s="3" t="n">
-        <v>-1</v>
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="D315" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7531,19 +7552,19 @@
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7552,19 +7573,19 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7573,19 +7594,19 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7594,19 +7615,19 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7615,19 +7636,19 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7636,19 +7657,19 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7657,19 +7678,19 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7678,19 +7699,19 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7699,19 +7720,19 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7720,19 +7741,19 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7741,19 +7762,19 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7762,19 +7783,19 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7783,19 +7804,19 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7804,19 +7825,19 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7825,19 +7846,19 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7846,19 +7867,19 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -7867,19 +7888,19 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>0</v>
@@ -7888,19 +7909,19 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0</v>
@@ -7909,19 +7930,19 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E335" s="2" t="n">
         <v>0</v>
@@ -7930,64 +7951,64 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D336" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B336" s="2" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C336" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D336" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E336" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C337" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D337" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E337" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B338" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C338" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D338" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E338" s="2" t="n">
-        <v>0</v>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="339">
@@ -7998,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8082,7 +8103,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
@@ -8098,19 +8119,19 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8119,19 +8140,19 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8140,19 +8161,19 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8161,19 +8182,19 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8182,19 +8203,19 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8203,19 +8224,19 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8224,19 +8245,19 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8245,12 +8266,12 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
@@ -8266,61 +8287,61 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="4" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B353" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C353" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D353" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E353" s="4" t="n">
-        <v>1</v>
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D353" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8329,19 +8350,19 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8350,19 +8371,19 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8371,19 +8392,19 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8392,19 +8413,19 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8413,19 +8434,19 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8434,19 +8455,19 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8455,19 +8476,19 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8476,19 +8497,19 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
@@ -8497,19 +8518,19 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0</v>
@@ -8518,19 +8539,19 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D364" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E364" s="2" t="n">
         <v>0</v>
@@ -8539,19 +8560,19 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E365" s="2" t="n">
         <v>0</v>
@@ -8560,19 +8581,19 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C366" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E366" s="2" t="n">
         <v>0</v>
@@ -8581,12 +8602,12 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
@@ -8602,19 +8623,19 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0</v>
@@ -8623,19 +8644,19 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8644,19 +8665,19 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8665,19 +8686,19 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -8686,7 +8707,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -8695,10 +8716,10 @@
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E372" s="2" t="n">
         <v>0</v>
@@ -8707,19 +8728,19 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E373" s="2" t="n">
         <v>0</v>
@@ -8728,19 +8749,19 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
@@ -8749,43 +8770,43 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="inlineStr">
-        <is>
-          <t>雷克萨斯</t>
-        </is>
-      </c>
-      <c r="B376" s="2" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C376" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D376" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E376" s="2" t="n">
-        <v>0</v>
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>阿斯顿·马丁</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E376" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -8796,7 +8817,7 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
@@ -8817,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8922,119 +8943,119 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D383" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E383" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E386" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D383" s="2" t="n">
+      <c r="D387" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E383" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B384" s="3" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C384" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="D384" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E384" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B385" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C385" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="D385" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="E385" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B386" s="3" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C386" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D386" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="E386" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B387" s="3" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C387" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="D387" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="E387" s="3" t="n">
-        <v>-1</v>
+      <c r="E387" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9043,19 +9064,19 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9064,19 +9085,19 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9085,19 +9106,19 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9106,19 +9127,19 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9127,19 +9148,19 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9148,19 +9169,19 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9169,19 +9190,19 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9190,19 +9211,19 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9211,19 +9232,19 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9232,19 +9253,19 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9253,19 +9274,19 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9274,19 +9295,19 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D400" s="2" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E400" s="2" t="n">
         <v>0</v>
@@ -9295,19 +9316,19 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9316,19 +9337,19 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9337,19 +9358,19 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D403" s="2" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E403" s="2" t="n">
         <v>0</v>
@@ -9358,19 +9379,19 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D404" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E404" s="2" t="n">
         <v>0</v>
@@ -9379,19 +9400,19 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C405" s="2" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D405" s="2" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="E405" s="2" t="n">
         <v>0</v>
@@ -9400,12 +9421,12 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
@@ -9419,87 +9440,87 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="inlineStr">
+      <c r="A407" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="E407" s="2" t="n">
-        <v>0</v>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="E408" s="2" t="n">
-        <v>0</v>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="inlineStr">
+      <c r="A409" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B409" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C409" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="D409" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="E409" s="2" t="n">
-        <v>0</v>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="inlineStr">
+      <c r="A410" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="2" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C410" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D410" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E410" s="2" t="n">
-        <v>0</v>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="411">
@@ -9510,79 +9531,562 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E413" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E416" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E417" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E418" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E422" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E425" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E426" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E427" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="E428" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E429" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E430" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E433" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C411" s="2" t="n">
+      <c r="C434" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D411" s="2" t="n">
+      <c r="D434" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E411" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="4" t="inlineStr">
+      <c r="E434" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B412" s="4" t="inlineStr">
+      <c r="B435" s="4" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C412" s="4" t="n">
+      <c r="C435" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="D412" s="4" t="n">
+      <c r="D435" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E412" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="4" t="inlineStr">
+      <c r="E435" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B413" s="4" t="inlineStr">
+      <c r="B436" s="4" t="inlineStr">
         <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C413" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="D413" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="E413" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="4" t="inlineStr">
+      <c r="E436" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B414" s="4" t="inlineStr">
+      <c r="B437" s="4" t="inlineStr">
         <is>
           <t>内蒙古</t>
         </is>
       </c>
-      <c r="C414" s="4" t="n">
+      <c r="C437" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D414" s="4" t="n">
+      <c r="D437" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="E414" s="4" t="n">
+      <c r="E437" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9840,7 +10344,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海康桥路销售中心</t>
+          <t>小鹏汽车上海虹梅南路销售中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9855,7 +10359,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区康桥路700-800号</t>
+          <t>上海市闵行区虹梅南路3398号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -9872,7 +10376,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海虹梅南路销售中心</t>
+          <t>小鹏汽车上海康桥路销售中心</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9887,7 +10391,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区虹梅南路3398号</t>
+          <t>上海市浦东新区康桥路700-800号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11110,7 +11614,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SAIC尚界用户中心•营口沈营公路</t>
+          <t>鸿蒙智行授权用户中心•营口工农路</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11125,7 +11629,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>营口市站前区沈营公路1号</t>
+          <t>营口市老边区新营路北15甲</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -11142,7 +11646,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•营口工农路</t>
+          <t>SAIC尚界用户中心•营口沈营公路</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11157,7 +11661,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>营口市老边区新营路北15甲</t>
+          <t>营口市站前区沈营公路1号</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -11255,22 +11759,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11280,7 +11784,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
@@ -11292,17 +11796,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11312,29 +11816,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11344,7 +11848,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
@@ -11356,17 +11860,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11376,7 +11880,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
@@ -11388,17 +11892,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11408,29 +11912,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11440,7 +11944,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
@@ -11548,17 +12052,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 天津空港</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 天津空港</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11644,17 +12148,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 天津空港</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 天津空港</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11676,17 +12180,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
+          <t>小米汽车四川省绵阳市涪城区汽车博览中心零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
+          <t>小米汽车四川绵阳涪城区汽车博览中心零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11696,7 +12200,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 68%</t>
+          <t>地址相似度 89%</t>
         </is>
       </c>
     </row>
@@ -11708,17 +12212,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区汽车博览中心零售中心</t>
+          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川绵阳涪城区汽车博览中心零售中心</t>
+          <t>小米之家湖北省黄冈市武穴市武穴万达汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11728,7 +12232,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 89%</t>
+          <t>地址相似度 68%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -11759,22 +11759,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
@@ -11823,22 +11823,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11860,17 +11860,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11880,29 +11880,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11912,29 +11912,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
@@ -11956,17 +11956,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
@@ -12052,17 +12052,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 许昌恒力汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12084,17 +12084,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
+          <t>蔚来空间 | 天津空港</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽车园</t>
+          <t>蔚来体验中心 | 天津空港</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12148,17 +12148,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 天津空港</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 天津空港</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -11614,7 +11614,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•营口工农路</t>
+          <t>SAIC尚界用户中心•营口沈营公路</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>营口市老边区新营路北15甲</t>
+          <t>营口市站前区沈营公路1号</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SAIC尚界用户中心•营口沈营公路</t>
+          <t>鸿蒙智行授权用户中心•营口工农路</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>营口市站前区沈营公路1号</t>
+          <t>营口市老边区新营路北15甲</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -11796,17 +11796,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
@@ -11860,17 +11860,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11880,29 +11880,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11912,29 +11912,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11944,29 +11944,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -11759,22 +11759,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
@@ -11796,17 +11796,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11816,29 +11816,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
@@ -11860,17 +11860,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11919,22 +11919,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11944,29 +11944,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11976,29 +11976,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路</t>
+          <t>湖州东吴银泰城体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
+          <t>湖州东吴银泰城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12008,29 +12008,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路 → 小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
+          <t>湖州东吴银泰城体验店 → 湖州东吴银泰城</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城体验店</t>
+          <t>小米汽车内蒙古包头市九原区稀土路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城</t>
+          <t>小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城体验店 → 湖州东吴银泰城</t>
+          <t>小米汽车内蒙古包头市九原区稀土路 → 小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
         </is>
       </c>
     </row>
@@ -12052,17 +12052,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
+          <t>蔚来中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽车园</t>
+          <t>蔚来体验中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 台州方林汽车城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 台州方林汽车城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12148,17 +12148,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 许昌恒力汽车园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260921_vs_20260928.xlsx
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海虹梅南路销售中心</t>
+          <t>小鹏汽车上海康桥路销售中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>上海市闵行区虹梅南路3398号</t>
+          <t>上海市浦东新区康桥路700-800号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车上海康桥路销售中心</t>
+          <t>小鹏汽车上海虹梅南路销售中心</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东新区康桥路700-800号</t>
+          <t>上海市闵行区虹梅南路3398号</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -11759,22 +11759,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>邯郸北环路特斯拉中心</t>
+          <t>小鹏汽车琼海豪华路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
+          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11796,17 +11796,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车常德大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11816,29 +11816,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
+          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11848,29 +11848,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
+          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车琼海豪华路销售服务中心</t>
+          <t>小米汽车山东省日照市东港区奎山汽车城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省琼海市嘉积镇豪华路59号 → 海南省琼海市嘉积镇豪华路59号小鹏汽车</t>
+          <t>奎山汽车城柳州路北、和阳南路西侧 → 日照市奎山汽车城柳州路北、和阳南路西侧</t>
         </is>
       </c>
     </row>
@@ -11892,17 +11892,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-2号</t>
+          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
         </is>
       </c>
     </row>
@@ -11924,17 +11924,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11944,29 +11944,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏交付中心 → 抚州市临川区临川大道小鹏服务中心</t>
+          <t>融创茂文旅城 → 重庆市大学城融创茂</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德大道销售服务中心</t>
+          <t>邯郸北环路特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11976,29 +11976,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖南省常德市武陵区常德大道1888号 → 武陵区常德大道1888号</t>
+          <t>河北省邯郸市北环路88号 → 河北省邯郸市复兴区北环路88号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城体验店</t>
+          <t>小米汽车内蒙古包头市九原区稀土路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城</t>
+          <t>小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12008,29 +12008,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖州东吴银泰城体验店 → 湖州东吴银泰城</t>
+          <t>小米汽车内蒙古包头市九原区稀土路 → 小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路</t>
+          <t>湖州东吴银泰城体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
+          <t>湖州东吴银泰城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车内蒙古包头市九原区稀土路 → 小米汽车内蒙古包头市九原区稀土路销售服务中心</t>
+          <t>湖州东吴银泰城体验店 → 湖州东吴银泰城</t>
         </is>
       </c>
     </row>
@@ -12052,17 +12052,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 台州方林汽车城</t>
+          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 台州方林汽车城</t>
+          <t>蔚来体验中心 | 许昌恒力汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12084,17 +12084,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 天津空港</t>
+          <t>蔚来中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 天津空港</t>
+          <t>蔚来体验中心 | 台州方林汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 天津空港</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 天津空港</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12148,17 +12148,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽贸城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 许昌恒力汽车园</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
